--- a/CSC 4500 GitHub/Employees.xlsx
+++ b/CSC 4500 GitHub/Employees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\AU\CSC 4500 GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{68DE1A36-46DC-44ED-ACD7-77C5C23AD5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE41941F-9F1C-4D9D-B07F-337C856FB274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="1260" windowWidth="21765" windowHeight="13560" xr2:uid="{620D3336-13B9-4639-8A03-C1386B546856}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{620D3336-13B9-4639-8A03-C1386B546856}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>Name</t>
   </si>
@@ -116,6 +116,18 @@
   </si>
   <si>
     <t>(815) 555-0110</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>Sales</t>
   </si>
 </sst>
 </file>
@@ -976,15 +988,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0180AC25-0E1C-4BAD-B8BC-ABA58B0364BA}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
     <col min="2" max="2" width="41.7109375" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -994,8 +1007,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1005,8 +1021,11 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1016,8 +1035,11 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1027,8 +1049,11 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1038,8 +1063,11 @@
       <c r="C5" t="s">
         <v>14</v>
       </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1049,8 +1077,11 @@
       <c r="C6" t="s">
         <v>17</v>
       </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1060,8 +1091,11 @@
       <c r="C7" t="s">
         <v>20</v>
       </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1071,8 +1105,11 @@
       <c r="C8" t="s">
         <v>22</v>
       </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1082,8 +1119,11 @@
       <c r="C9" t="s">
         <v>25</v>
       </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1093,8 +1133,11 @@
       <c r="C10" t="s">
         <v>28</v>
       </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1103,6 +1146,9 @@
       </c>
       <c r="C11" t="s">
         <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/CSC 4500 GitHub/Employees.xlsx
+++ b/CSC 4500 GitHub/Employees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\AU\CSC 4500 GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE41941F-9F1C-4D9D-B07F-337C856FB274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA22D90E-611B-4E8F-8821-4FD2C292BC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{620D3336-13B9-4639-8A03-C1386B546856}"/>
+    <workbookView xWindow="1020" yWindow="1260" windowWidth="14910" windowHeight="11730" xr2:uid="{620D3336-13B9-4639-8A03-C1386B546856}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Name</t>
   </si>
@@ -118,16 +118,7 @@
     <t>(815) 555-0110</t>
   </si>
   <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Human Resources</t>
-  </si>
-  <si>
-    <t>Information Technology</t>
-  </si>
-  <si>
-    <t>Sales</t>
+    <t>Department ID</t>
   </si>
 </sst>
 </file>
@@ -994,7 +985,7 @@
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
     <col min="2" max="2" width="41.7109375" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1021,8 +1012,8 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>33</v>
+      <c r="D2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1035,8 +1026,8 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>34</v>
+      <c r="D3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1049,8 +1040,8 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>33</v>
+      <c r="D4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1063,8 +1054,8 @@
       <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
-        <v>35</v>
+      <c r="D5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1077,8 +1068,8 @@
       <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
-        <v>34</v>
+      <c r="D6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1091,8 +1082,8 @@
       <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
-        <v>35</v>
+      <c r="D7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1105,8 +1096,8 @@
       <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
-        <v>33</v>
+      <c r="D8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,8 +1110,8 @@
       <c r="C9" t="s">
         <v>25</v>
       </c>
-      <c r="D9" t="s">
-        <v>35</v>
+      <c r="D9">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1133,8 +1124,8 @@
       <c r="C10" t="s">
         <v>28</v>
       </c>
-      <c r="D10" t="s">
-        <v>34</v>
+      <c r="D10">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1147,8 +1138,8 @@
       <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
-        <v>34</v>
+      <c r="D11">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/CSC 4500 GitHub/Employees.xlsx
+++ b/CSC 4500 GitHub/Employees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\AU\CSC 4500 GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA22D90E-611B-4E8F-8821-4FD2C292BC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069EFEDC-620B-4A6D-915E-64D9C61265EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="1260" windowWidth="14910" windowHeight="11730" xr2:uid="{620D3336-13B9-4639-8A03-C1386B546856}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{620D3336-13B9-4639-8A03-C1386B546856}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>Name</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>Department ID</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
   </si>
 </sst>
 </file>
@@ -979,166 +982,200 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0180AC25-0E1C-4BAD-B8BC-ABA58B0364BA}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="2" max="2" width="41.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>17</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1006</v>
+      </c>
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1007</v>
+      </c>
+      <c r="B8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1008</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>25</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1009</v>
+      </c>
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>27</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>28</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1010</v>
+      </c>
+      <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>31</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>2</v>
       </c>
     </row>

--- a/CSC 4500 GitHub/Employees.xlsx
+++ b/CSC 4500 GitHub/Employees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\AU\CSC 4500 GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069EFEDC-620B-4A6D-915E-64D9C61265EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D892A0-3C21-4002-A1F9-34F468171BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{620D3336-13B9-4639-8A03-C1386B546856}"/>
+    <workbookView xWindow="-28365" yWindow="495" windowWidth="21600" windowHeight="11235" xr2:uid="{620D3336-13B9-4639-8A03-C1386B546856}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -445,7 +445,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -560,6 +560,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -605,8 +620,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -982,200 +998,200 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0180AC25-0E1C-4BAD-B8BC-ABA58B0364BA}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B3:F13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="41.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F3" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
         <v>1001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2">
+      <c r="F4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
         <v>1002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3">
+      <c r="F5" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
         <v>1003</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E4">
+      <c r="F6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
         <v>1004</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5">
+      <c r="F7" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
         <v>1005</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E6">
+      <c r="F8" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
         <v>1006</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E7">
+      <c r="F9" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
         <v>1007</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E8">
+      <c r="F10" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
         <v>1008</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E9">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
         <v>1009</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E10">
+      <c r="F12" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
         <v>1010</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E11">
+      <c r="F13" s="1">
         <v>2</v>
       </c>
     </row>
